--- a/output/pdf_financials_xlsx/RRRL.xlsx
+++ b/output/pdf_financials_xlsx/RRRL.xlsx
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.024166</v>
       </c>
     </row>
     <row r="93">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-0.065</v>
+        <v>-0.003135</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-0.021565</v>
@@ -2496,7 +2496,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2962,7 +2966,11 @@
           <t>Exploration and evaluation expenditures in AP</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.061865</v>
       </c>

--- a/output/pdf_financials_xlsx/RRRL.xlsx
+++ b/output/pdf_financials_xlsx/RRRL.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.221361</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.200664</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.221361</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.200664</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.231361</v>
+        <v>0.01</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.211634</v>
+        <v>0.01097</v>
       </c>
     </row>
     <row r="49">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/RRRL.xlsx
+++ b/output/pdf_financials_xlsx/RRRL.xlsx
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.091317</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.014159</v>
       </c>
     </row>
     <row r="65">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.030556</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="68">
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.018296</v>
       </c>
     </row>
     <row r="102">
@@ -1818,7 +1818,7 @@
         <v>0.047657</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.093684</v>
+        <v>-0.11198</v>
       </c>
     </row>
     <row r="107">
@@ -2690,7 +2690,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
